--- a/output/pdf_financials_xlsx/NTR.xlsx
+++ b/output/pdf_financials_xlsx/NTR.xlsx
@@ -5080,7 +5080,7 @@
         <v>-1728</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-2475</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>-2600</v>
@@ -5089,7 +5089,7 @@
         <v>-2154</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-2005</v>
       </c>
     </row>
     <row r="135">
@@ -5108,7 +5108,7 @@
         <v>1937</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>8110</v>
+        <v>5635</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>2466</v>
@@ -5117,7 +5117,7 @@
         <v>1381</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>4007</v>
+        <v>2002</v>
       </c>
     </row>
   </sheetData>
@@ -5975,7 +5975,11 @@
           <t>Capital expenditures1 14, 15</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -9580,7 +9584,11 @@
           <t>Capital expenditures1 13, 14</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -20778,7 +20786,11 @@
           <t>General and administrative expenses Note 5</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E313" s="5" t="n">
         <v>-185</v>
       </c>

--- a/output/pdf_financials_xlsx/NTR.xlsx
+++ b/output/pdf_financials_xlsx/NTR.xlsx
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>694</v>
+        <v>4547</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>19636</v>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>3316</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>13380</v>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-0.014844</v>
+        <v>-125</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>43</v>
@@ -1176,10 +1176,8 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>840.316</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>624.9</v>
@@ -1291,7 +1289,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-4.178674351585014</v>
+        <v>-0.6377831537277325</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>7.476064371562437</v>
@@ -1347,7 +1345,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>47.11815561959654</v>
+        <v>7.191554871343743</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>18.19617029944999</v>
@@ -4413,7 +4411,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-651</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>-1405</v>
@@ -4833,7 +4831,7 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>0</v>
+        <v>-330</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>-952</v>
@@ -5071,7 +5069,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-651</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>-1405</v>
@@ -5099,7 +5097,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>1225</v>
+        <v>574</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>647</v>
@@ -13570,7 +13568,11 @@
           <t>Adjustments to reconcile net earnings to cash provided by operating activities Note 12</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E169" s="5" t="n">
         <v>826</v>
       </c>
@@ -13827,7 +13829,11 @@
           <t>Additions to property, plant and equipment Note 16</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E174" s="5" t="n">
         <v>-651</v>
       </c>
@@ -14237,7 +14243,11 @@
           <t>Dividends paid Note 24</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E182" s="5" t="n">
         <v>-330</v>
       </c>
@@ -20557,7 +20567,11 @@
           <t>SALES Note 4 $</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E308" s="5" t="n">
         <v>4547</v>
       </c>
@@ -20647,12 +20661,16 @@
           <t>Cost of goods sold Note 5</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E310" s="5" t="n">
-        <v>-3316</v>
+        <v>3316</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>-13380</v>
+        <v>13380</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -20741,7 +20759,11 @@
           <t>Selling expenses Note 5</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SellingExpense</t>
+        </is>
+      </c>
       <c r="E312" s="5" t="n">
         <v>-29</v>
       </c>
@@ -20927,7 +20949,11 @@
           <t>Other expenses Note 7</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E316" s="5" t="n">
         <v>-125</v>
       </c>
@@ -21438,12 +21464,16 @@
           <t>Weighted average shares outstanding for diluted EPS Note 11</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E327" s="5" t="n">
-        <v>840316000</v>
+        <v>840.316</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>624900000</v>
+        <v>624.9</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NTR.xlsx
+++ b/output/pdf_financials_xlsx/NTR.xlsx
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>694</v>
+        <v>209</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>5392</v>
+        <v>414</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5441</v>
+        <v>1862</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>15424</v>
+        <v>10809</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>8474</v>
+        <v>2745</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>7530</v>
+        <v>1856</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>8347</v>
+        <v>3736</v>
       </c>
     </row>
     <row r="12">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-209</v>
+        <v>-0.169817</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>93</v>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-720.6896551724138</v>
+        <v>-0.5855758620689655</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-75</v>
@@ -11277,7 +11277,11 @@
           <t>Additions to intangible assets 16</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -16265,7 +16269,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -17723,7 +17727,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -19559,7 +19563,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -21000,7 +21004,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E317" s="5" t="n">

--- a/output/pdf_financials_xlsx/NTR.xlsx
+++ b/output/pdf_financials_xlsx/NTR.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.169817</v>
+        <v>-183</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>93</v>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0.5855758620689655</v>
+        <v>-631.0344827586207</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-75</v>
@@ -4190,22 +4190,22 @@
         <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-238</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-1167</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>1376</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-557</v>
       </c>
     </row>
     <row r="104">
@@ -4271,13 +4271,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-1040</v>
+        <v>-1138</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>126</v>
+        <v>-112</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-44</v>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108">
@@ -4538,10 +4538,10 @@
         <v>7</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>7</v>
+        <v>138</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>838</v>
       </c>
     </row>
     <row r="116">
@@ -4694,22 +4694,22 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-1930</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-4520</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-1047</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-184</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-551</v>
       </c>
     </row>
     <row r="122">
@@ -5356,7 +5356,11 @@
           <t>Share-based compensation expense 7</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -5826,7 +5830,11 @@
           <t>Inventories and prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -6177,7 +6185,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -6610,7 +6622,11 @@
           <t>Repurchase of common shares 23</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11122,7 +11138,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -11948,7 +11968,11 @@
           <t>Repurchase of common shares 25</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -13625,7 +13649,11 @@
           <t>Changes in non-cash operating working capital Note 12</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E170" s="5" t="n">
         <v>72</v>
       </c>
@@ -14300,7 +14328,11 @@
           <t>Repurchase of common shares Note 24</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -21145,7 +21177,11 @@
           <t>Income tax recovery Note 9</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E320" s="5" t="n">
         <v>183</v>
       </c>
